--- a/artfynd/A 61574-2025 artfynd.xlsx
+++ b/artfynd/A 61574-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>437902</v>
+        <v>419117</v>
       </c>
       <c r="B2" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,26 +703,17 @@
           <t>Knaben</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Harg Ekdalen, 680 m NNV-ut, Upl</t>
+          <t>Ekdalen, 570 m N om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>686304.5886820774</v>
+        <v>686248</v>
       </c>
       <c r="R2" t="n">
-        <v>6667482.355850763</v>
+        <v>6667303</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,29 +738,24 @@
           <t>Harg</t>
         </is>
       </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>C-ÖST-0523</t>
+        </is>
+      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-06-06</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-06-06</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hot: övertäckning med barrförna. Åtgärd: träd tas bort</t>
+          <t>Ekdalen 500 m NNV -ut 6667340 1641570 10 m / Strödda ex.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,37 +769,32 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>klipphäll mot vägkant</t>
+          <t>Väghällar</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Svenson, Ebbe Zachrisson</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>ÅGP hällebräcka C-län</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>438177</v>
+        <v>419118</v>
       </c>
       <c r="B3" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,21 +820,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Harg Ekdalen, 800 m NNV-ut, Upl</t>
+          <t>Ekdalen, 800 m NNV om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>686331.9972303597</v>
+        <v>686332</v>
       </c>
       <c r="R3" t="n">
-        <v>6667543.691460172</v>
+        <v>6667544</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,33 +854,28 @@
           <t>Harg</t>
         </is>
       </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>C-ÖST-0525</t>
+        </is>
+      </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-01-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-06-06</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1999-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Funnen 1999, strödda ex av Ebbe Zachrisson</t>
+          <t>Strödda ex.</t>
         </is>
       </c>
       <c r="AD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
@@ -919,37 +885,32 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>skogsbilväg</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anders Svenson</t>
+          <t>Floraväkterisamordn C-län</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Svenson, Ebbe Zachrisson</t>
+          <t>Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>ÅGP hällebräcka C-län</t>
+          <t>Floraväkteri Sverige</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>430831</v>
+        <v>430832</v>
       </c>
       <c r="B4" t="n">
-        <v>99120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,7 +937,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>182</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -986,14 +947,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Harg Ekdalen, 570 m N-ut, Upl</t>
+          <t>Harg Ekdalen, 680 m NNV-ut, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>686247.660258587</v>
+        <v>686305</v>
       </c>
       <c r="R4" t="n">
-        <v>6667302.625847778</v>
+        <v>6667482</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1023,24 +984,9 @@
           <t>2006-06-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2006-06-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Tidigare angiven med Ekdalen 500 m N-ut 6667340 1641570 10 m väghällar. Funnen 1999, strödda ex av Ebbe Zachrisson</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,12 +1025,7 @@
         <v>121430755</v>
       </c>
       <c r="B5" t="n">
-        <v>100991</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1171,7 +1112,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Hellkvist, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Emma Hellkvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 61574-2025 artfynd.xlsx
+++ b/artfynd/A 61574-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/419117</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/419118</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1019,6 +1034,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/430832</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,8 +1136,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430755</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>